--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Sprint3_Burndown.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2. Metodología Scrum/SPRINTS/SITRAFO_Sprint3_Burndown.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Burndown" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>SITRAFO — Control del Sprint 3 (sprint de cierre de la Fase 2)</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Día 5 (21 oct)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Día 6 (22 oct)</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1012,7 @@
         <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>10</v>
@@ -1410,7 +1413,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -1428,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5">
         <v>0</v>
@@ -1455,7 +1458,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5">
         <v>0</v>
@@ -1680,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
@@ -1704,7 +1707,7 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
@@ -1722,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
@@ -1880,7 +1883,6 @@
       </c>
       <c r="B26" s="8">
         <f>B23</f>
-        <v>105</v>
       </c>
       <c r="C26" s="8">
         <f t="shared" ref="C26:L26" si="2">B26-C23</f>
@@ -1929,47 +1931,36 @@
       </c>
       <c r="B27" s="8">
         <f>B23</f>
-        <v>105</v>
       </c>
       <c r="C27" s="8">
         <f>ROUND($B$23-$B$23/10*1,1)</f>
-        <v>94.5</v>
       </c>
       <c r="D27" s="8">
         <f>ROUND($B$23-$B$23/10*2,1)</f>
-        <v>84</v>
       </c>
       <c r="E27" s="8">
         <f>ROUND($B$23-$B$23/10*3,1)</f>
-        <v>73.5</v>
       </c>
       <c r="F27" s="8">
         <f>ROUND($B$23-$B$23/10*4,1)</f>
-        <v>63</v>
       </c>
       <c r="G27" s="8">
         <f>ROUND($B$23-$B$23/10*5,1)</f>
-        <v>52.5</v>
       </c>
       <c r="H27" s="8">
         <f>ROUND($B$23-$B$23/10*6,1)</f>
-        <v>42</v>
       </c>
       <c r="I27" s="8">
         <f>ROUND($B$23-$B$23/10*7,1)</f>
-        <v>31.5</v>
       </c>
       <c r="J27" s="8">
         <f>ROUND($B$23-$B$23/10*8,1)</f>
-        <v>21</v>
       </c>
       <c r="K27" s="8">
         <f>ROUND($B$23-$B$23/10*9,1)</f>
-        <v>10.5</v>
       </c>
       <c r="L27" s="8">
         <f>ROUND($B$23-$B$23/10*10,1)</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
